--- a/Kimutatás - napi adatok 2025.08.22-ig_háttértábla.xlsx
+++ b/Kimutatás - napi adatok 2025.08.22-ig_háttértábla.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\SZIG\UKO\_Vezetoseg\Riportok\SZO Kapacitás tábla - ÜKO rész\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B483EB-F2E6-4260-A52D-CFC0CBC82341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB811196-067D-4096-9BE4-5825D7079F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,8 +26,8 @@
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <customWorkbookViews>
+    <customWorkbookView name="Csikós Erzsébet - Egyéni nézet" guid="{8D9F0278-BE1A-4C9D-9000-646DE54612AB}" mergeInterval="0" personalView="1" maximized="1" xWindow="4472" yWindow="-8" windowWidth="1936" windowHeight="1056" tabRatio="729" activeSheetId="1"/>
     <customWorkbookView name="Sándor László - Egyéni nézet" guid="{10E533D9-5244-424B-8F3E-28E3FF755EE9}" mergeInterval="0" personalView="1" maximized="1" xWindow="-2568" yWindow="-198" windowWidth="2576" windowHeight="1408" tabRatio="729" activeSheetId="1"/>
-    <customWorkbookView name="Csikós Erzsébet - Egyéni nézet" guid="{8D9F0278-BE1A-4C9D-9000-646DE54612AB}" mergeInterval="0" personalView="1" maximized="1" xWindow="4472" yWindow="-8" windowWidth="1936" windowHeight="1056" tabRatio="729" activeSheetId="1"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -364,7 +364,7 @@
       <charset val="238"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -464,12 +464,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1014,7 +1008,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="18" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1203,10 +1197,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$1:$AL$1</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$1:$AM$1</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46027</c:v>
                 </c:pt>
@@ -1305,16 +1299,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46069</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46070</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$2:$AL$2</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$2:$AM$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>498</c:v>
                 </c:pt>
@@ -1413,6 +1410,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>1216</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>406</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1507,10 +1507,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$1:$AL$1</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$1:$AM$1</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46027</c:v>
                 </c:pt>
@@ -1609,16 +1609,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46069</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46070</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$3:$AL$3</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$3:$AM$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>1890</c:v>
                 </c:pt>
@@ -1717,6 +1720,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>2400</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3030</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1811,10 +1817,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$1:$AL$1</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$1:$AM$1</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46027</c:v>
                 </c:pt>
@@ -1913,16 +1919,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46069</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46070</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$4:$AL$4</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$4:$AM$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>425</c:v>
                 </c:pt>
@@ -2021,6 +2030,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>701</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>626</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2117,10 +2129,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$1:$AL$1</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$1:$AM$1</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46027</c:v>
                 </c:pt>
@@ -2219,16 +2231,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46069</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46070</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$5:$AL$5</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$5:$AM$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>733</c:v>
                 </c:pt>
@@ -2327,6 +2342,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>621</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>473</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2423,10 +2441,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$1:$AL$1</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$1:$AM$1</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46027</c:v>
                 </c:pt>
@@ -2525,16 +2543,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46069</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46070</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$6:$AL$6</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$6:$AM$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>97</c:v>
                 </c:pt>
@@ -2633,6 +2654,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2744,10 +2768,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$1:$AL$1</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$1:$AM$1</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46027</c:v>
                 </c:pt>
@@ -2846,16 +2870,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46069</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46070</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$7:$AL$7</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$7:$AM$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>2388</c:v>
                 </c:pt>
@@ -2954,6 +2981,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>3616</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3436</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3053,10 +3083,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$1:$AL$1</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$1:$AM$1</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46027</c:v>
                 </c:pt>
@@ -3155,16 +3185,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46069</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46070</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$8:$AL$8</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$8:$AM$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>572</c:v>
                 </c:pt>
@@ -3263,6 +3296,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>639</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>457</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20325,7 +20361,9 @@
       <c r="AL2" s="104">
         <v>1216</v>
       </c>
-      <c r="AM2" s="122"/>
+      <c r="AM2" s="104">
+        <v>406</v>
+      </c>
       <c r="AN2" s="122"/>
       <c r="AO2" s="122"/>
       <c r="AP2" s="122"/>
@@ -20437,7 +20475,9 @@
       <c r="AL3" s="104">
         <v>2400</v>
       </c>
-      <c r="AM3" s="122"/>
+      <c r="AM3" s="104">
+        <v>3030</v>
+      </c>
       <c r="AN3" s="122"/>
       <c r="AO3" s="122"/>
       <c r="AP3" s="122"/>
@@ -20549,7 +20589,9 @@
       <c r="AL4" s="104">
         <v>701</v>
       </c>
-      <c r="AM4" s="122"/>
+      <c r="AM4" s="104">
+        <v>626</v>
+      </c>
       <c r="AN4" s="122"/>
       <c r="AO4" s="122"/>
       <c r="AP4" s="122"/>
@@ -20661,7 +20703,9 @@
       <c r="AL5" s="104">
         <v>621</v>
       </c>
-      <c r="AM5" s="122"/>
+      <c r="AM5" s="104">
+        <v>473</v>
+      </c>
       <c r="AN5" s="122"/>
       <c r="AO5" s="122"/>
       <c r="AP5" s="122"/>
@@ -20773,7 +20817,9 @@
       <c r="AL6" s="104">
         <v>149</v>
       </c>
-      <c r="AM6" s="122"/>
+      <c r="AM6" s="104">
+        <v>126</v>
+      </c>
       <c r="AN6" s="122"/>
       <c r="AO6" s="122"/>
       <c r="AP6" s="122"/>
@@ -20885,7 +20931,9 @@
       <c r="AL7" s="104">
         <v>3616</v>
       </c>
-      <c r="AM7" s="122"/>
+      <c r="AM7" s="104">
+        <v>3436</v>
+      </c>
       <c r="AN7" s="122"/>
       <c r="AO7" s="122"/>
       <c r="AP7" s="122"/>
@@ -20997,7 +21045,9 @@
       <c r="AL8" s="104">
         <v>639</v>
       </c>
-      <c r="AM8" s="122"/>
+      <c r="AM8" s="104">
+        <v>457</v>
+      </c>
       <c r="AN8" s="122"/>
       <c r="AO8" s="122"/>
       <c r="AP8" s="122"/>
@@ -34030,12 +34080,12 @@
     </row>
   </sheetData>
   <customSheetViews>
+    <customSheetView guid="{8D9F0278-BE1A-4C9D-9000-646DE54612AB}" topLeftCell="A53">
+      <selection activeCell="M114" sqref="M114"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
     <customSheetView guid="{10E533D9-5244-424B-8F3E-28E3FF755EE9}" topLeftCell="A143">
       <selection activeCell="Q173" sqref="Q173"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-    </customSheetView>
-    <customSheetView guid="{8D9F0278-BE1A-4C9D-9000-646DE54612AB}" topLeftCell="A53">
-      <selection activeCell="M114" sqref="M114"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
   </customSheetViews>
@@ -45334,15 +45384,15 @@
     </row>
   </sheetData>
   <customSheetViews>
+    <customSheetView guid="{8D9F0278-BE1A-4C9D-9000-646DE54612AB}" scale="50" hiddenColumns="1">
+      <pane xSplit="225" topLeftCell="JU1" activePane="topRight" state="frozen"/>
+      <selection pane="topRight" activeCell="KW12" sqref="KW12"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+    </customSheetView>
     <customSheetView guid="{10E533D9-5244-424B-8F3E-28E3FF755EE9}" scale="85" hiddenColumns="1">
       <pane xSplit="225" topLeftCell="JU1" activePane="topRight" state="frozen"/>
       <selection pane="topRight" activeCell="MT25" sqref="MT25"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-    </customSheetView>
-    <customSheetView guid="{8D9F0278-BE1A-4C9D-9000-646DE54612AB}" scale="50" hiddenColumns="1">
-      <pane xSplit="225" topLeftCell="JU1" activePane="topRight" state="frozen"/>
-      <selection pane="topRight" activeCell="KW12" sqref="KW12"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId2"/>
     </customSheetView>
@@ -48446,13 +48496,13 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{10E533D9-5244-424B-8F3E-28E3FF755EE9}">
+    <customSheetView guid="{8D9F0278-BE1A-4C9D-9000-646DE54612AB}">
       <pane ySplit="1" topLeftCell="A92" activePane="bottomLeft" state="frozen"/>
       <selection pane="bottomLeft" activeCell="C146" sqref="C146"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
     </customSheetView>
-    <customSheetView guid="{8D9F0278-BE1A-4C9D-9000-646DE54612AB}">
+    <customSheetView guid="{10E533D9-5244-424B-8F3E-28E3FF755EE9}">
       <pane ySplit="1" topLeftCell="A92" activePane="bottomLeft" state="frozen"/>
       <selection pane="bottomLeft" activeCell="C146" sqref="C146"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52391,12 +52441,12 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{10E533D9-5244-424B-8F3E-28E3FF755EE9}" scale="80">
+    <customSheetView guid="{8D9F0278-BE1A-4C9D-9000-646DE54612AB}" scale="80">
       <pane xSplit="1" topLeftCell="BZ1" activePane="topRight" state="frozen"/>
       <selection pane="topRight" activeCell="DI51" sqref="DI51"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
-    <customSheetView guid="{8D9F0278-BE1A-4C9D-9000-646DE54612AB}" scale="80">
+    <customSheetView guid="{10E533D9-5244-424B-8F3E-28E3FF755EE9}" scale="80">
       <pane xSplit="1" topLeftCell="BZ1" activePane="topRight" state="frozen"/>
       <selection pane="topRight" activeCell="DI51" sqref="DI51"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52408,21 +52458,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentum" ma:contentTypeID="0x010100128194314371734C945217DA74598295" ma:contentTypeVersion="2" ma:contentTypeDescription="Új dokumentum létrehozása." ma:contentTypeScope="" ma:versionID="1c8180ff78bb090cc177689f93f7b063">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1649870-1b63-4afc-979e-80a69c95e2e0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9f88221a4541e9375d5ee7c2624bcea" ns2:_="">
     <xsd:import namespace="d1649870-1b63-4afc-979e-80a69c95e2e0"/>
@@ -52570,31 +52605,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D27633-6610-41F1-9A2D-A3B8AB060590}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d1649870-1b63-4afc-979e-80a69c95e2e0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7080305-EACD-492B-9489-FF8A41667880}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D68CDEFA-D59D-4F18-B41F-2FBDE4F84287}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -52610,4 +52636,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7080305-EACD-492B-9489-FF8A41667880}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D27633-6610-41F1-9A2D-A3B8AB060590}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d1649870-1b63-4afc-979e-80a69c95e2e0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Kimutatás - napi adatok 2025.08.22-ig_háttértábla.xlsx
+++ b/Kimutatás - napi adatok 2025.08.22-ig_háttértábla.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\SZIG\UKO\_Vezetoseg\Riportok\SZO Kapacitás tábla - ÜKO rész\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB811196-067D-4096-9BE4-5825D7079F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7E0F35-C41C-4753-AE31-2ECD85E85EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <definedName name="Z_10E533D9_5244_424B_8F3E_28E3FF755EE9_.wvu.Cols" localSheetId="3" hidden="1">'Napi kimutatás'!$B:$HR</definedName>
     <definedName name="Z_8D9F0278_BE1A_4C9D_9000_646DE54612AB_.wvu.Cols" localSheetId="3" hidden="1">'Napi kimutatás'!$B:$HR</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <customWorkbookViews>
     <customWorkbookView name="Csikós Erzsébet - Egyéni nézet" guid="{8D9F0278-BE1A-4C9D-9000-646DE54612AB}" mergeInterval="0" personalView="1" maximized="1" xWindow="4472" yWindow="-8" windowWidth="1936" windowHeight="1056" tabRatio="729" activeSheetId="1"/>
     <customWorkbookView name="Sándor László - Egyéni nézet" guid="{10E533D9-5244-424B-8F3E-28E3FF755EE9}" mergeInterval="0" personalView="1" maximized="1" xWindow="-2568" yWindow="-198" windowWidth="2576" windowHeight="1408" tabRatio="729" activeSheetId="1"/>
@@ -1007,8 +1007,10 @@
     <xf numFmtId="1" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1197,10 +1199,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$1:$AM$1</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$1:$BE$1</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46027</c:v>
                 </c:pt>
@@ -1302,16 +1304,70 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46070</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46071</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46072</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46073</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$2:$AM$2</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$2:$BE$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>498</c:v>
                 </c:pt>
@@ -1413,6 +1469,60 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>406</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>479</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>689</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1364</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1614</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2231</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1817</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1649</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2267</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2575</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2434</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1925</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1937</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2288</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1696</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>968</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>518</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>830</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1507,10 +1617,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$1:$AM$1</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$1:$BE$1</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46027</c:v>
                 </c:pt>
@@ -1612,16 +1722,70 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46070</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46071</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46072</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46073</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$3:$AM$3</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$3:$BE$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>1890</c:v>
                 </c:pt>
@@ -1723,6 +1887,60 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>3030</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2656</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2292</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2072</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1651</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2503</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3090</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2989</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2657</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2862</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3396</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3198</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3005</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3676</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4077</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4360</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>4070</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>3620</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1817,10 +2035,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$1:$AM$1</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$1:$BE$1</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46027</c:v>
                 </c:pt>
@@ -1922,16 +2140,70 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46070</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46071</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46072</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46073</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$4:$AM$4</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$4:$BE$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>425</c:v>
                 </c:pt>
@@ -2033,6 +2305,60 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>626</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>843</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>766</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>548</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>588</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>770</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>486</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>481</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>479</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>882</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>885</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>836</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>898</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>729</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>773</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>833</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>783</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>838</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>574</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2129,10 +2455,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$1:$AM$1</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$1:$BE$1</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46027</c:v>
                 </c:pt>
@@ -2234,16 +2560,70 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46070</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46071</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46072</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46073</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$5:$AM$5</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$5:$BE$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>733</c:v>
                 </c:pt>
@@ -2345,6 +2725,60 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>473</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>539</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>490</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>572</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>704</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>605</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>523</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>646</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>580</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>788</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>530</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>499</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>568</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>479</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>666</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>599</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>545</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2441,10 +2875,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$1:$AM$1</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$1:$BE$1</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46027</c:v>
                 </c:pt>
@@ -2546,16 +2980,70 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46070</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46071</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46072</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46073</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$6:$AM$6</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$6:$BE$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>97</c:v>
                 </c:pt>
@@ -2657,6 +3145,60 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>278</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>286</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>291</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>262</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>253</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>264</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>255</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>249</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>243</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>255</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>306</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2768,10 +3310,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$1:$AM$1</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$1:$BE$1</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46027</c:v>
                 </c:pt>
@@ -2873,16 +3415,70 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46070</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46071</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46072</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46073</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$7:$AM$7</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$7:$BE$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>2388</c:v>
                 </c:pt>
@@ -2984,6 +3580,60 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>3436</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3135</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2981</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3436</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3657</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3882</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>4320</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>4739</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>5256</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>5232</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>5296</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>5321</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>5135</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>5293</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>5372</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>5045</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4878</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>4900</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>4885</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3083,10 +3733,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$1:$AM$1</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$1:$BE$1</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46027</c:v>
                 </c:pt>
@@ -3188,16 +3838,70 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46070</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46071</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46072</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46073</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Napi kimutatás 2026'!$F$8:$AM$8</c:f>
+              <c:f>'Napi kimutatás 2026'!$F$8:$BE$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>572</c:v>
                 </c:pt>
@@ -3299,6 +4003,60 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>457</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>492</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>535</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>572</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>710</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>726</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>637</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>648</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>710</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>646</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>651</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>515</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>472</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>559</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>414</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>549</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>573</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>541</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17992,6 +18750,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -17999,7 +18758,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -20119,14 +20877,18 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:AP10"/>
+  <dimension ref="A1:BJ10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="42" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="43" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="15.42578125" customWidth="1"/>
+    <col min="45" max="52" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="53" max="57" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="58" max="62" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:62" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20223,19 +20985,19 @@
       <c r="AF1" s="97">
         <v>46059</v>
       </c>
-      <c r="AG1" s="123">
+      <c r="AG1" s="122">
         <v>46062</v>
       </c>
-      <c r="AH1" s="123">
+      <c r="AH1" s="122">
         <v>46063</v>
       </c>
-      <c r="AI1" s="123">
+      <c r="AI1" s="122">
         <v>46064</v>
       </c>
-      <c r="AJ1" s="123">
+      <c r="AJ1" s="122">
         <v>46065</v>
       </c>
-      <c r="AK1" s="123">
+      <c r="AK1" s="122">
         <v>46066</v>
       </c>
       <c r="AL1" s="97">
@@ -20253,8 +21015,68 @@
       <c r="AP1" s="97">
         <v>46073</v>
       </c>
-    </row>
-    <row r="2" spans="1:42" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AQ1" s="123">
+        <v>46076</v>
+      </c>
+      <c r="AR1" s="123">
+        <v>46077</v>
+      </c>
+      <c r="AS1" s="123">
+        <v>46078</v>
+      </c>
+      <c r="AT1" s="123">
+        <v>46079</v>
+      </c>
+      <c r="AU1" s="123">
+        <v>46080</v>
+      </c>
+      <c r="AV1" s="97">
+        <v>46083</v>
+      </c>
+      <c r="AW1" s="97">
+        <v>46084</v>
+      </c>
+      <c r="AX1" s="97">
+        <v>46085</v>
+      </c>
+      <c r="AY1" s="97">
+        <v>46086</v>
+      </c>
+      <c r="AZ1" s="97">
+        <v>46087</v>
+      </c>
+      <c r="BA1" s="123">
+        <v>46090</v>
+      </c>
+      <c r="BB1" s="123">
+        <v>46091</v>
+      </c>
+      <c r="BC1" s="123">
+        <v>46092</v>
+      </c>
+      <c r="BD1" s="123">
+        <v>46093</v>
+      </c>
+      <c r="BE1" s="123">
+        <v>46094</v>
+      </c>
+      <c r="BF1" s="97">
+        <v>46097</v>
+      </c>
+      <c r="BG1" s="97">
+        <v>46098</v>
+      </c>
+      <c r="BH1" s="97">
+        <v>46099</v>
+      </c>
+      <c r="BI1" s="97">
+        <v>46100</v>
+      </c>
+      <c r="BJ1" s="97">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:62" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -20364,11 +21186,67 @@
       <c r="AM2" s="104">
         <v>406</v>
       </c>
-      <c r="AN2" s="122"/>
-      <c r="AO2" s="122"/>
-      <c r="AP2" s="122"/>
-    </row>
-    <row r="3" spans="1:42" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AN2" s="104">
+        <v>479</v>
+      </c>
+      <c r="AO2" s="104">
+        <v>689</v>
+      </c>
+      <c r="AP2" s="104">
+        <v>1364</v>
+      </c>
+      <c r="AQ2" s="104">
+        <v>1614</v>
+      </c>
+      <c r="AR2" s="104">
+        <v>2231</v>
+      </c>
+      <c r="AS2" s="104">
+        <v>1817</v>
+      </c>
+      <c r="AT2" s="104">
+        <v>1649</v>
+      </c>
+      <c r="AU2" s="104">
+        <v>2267</v>
+      </c>
+      <c r="AV2" s="104">
+        <v>2575</v>
+      </c>
+      <c r="AW2" s="104">
+        <v>2434</v>
+      </c>
+      <c r="AX2" s="104">
+        <v>1925</v>
+      </c>
+      <c r="AY2" s="104">
+        <v>1937</v>
+      </c>
+      <c r="AZ2" s="104">
+        <v>2288</v>
+      </c>
+      <c r="BA2" s="104">
+        <v>1696</v>
+      </c>
+      <c r="BB2" s="104">
+        <v>968</v>
+      </c>
+      <c r="BC2" s="104">
+        <v>518</v>
+      </c>
+      <c r="BD2" s="104">
+        <v>830</v>
+      </c>
+      <c r="BE2" s="104">
+        <v>1265</v>
+      </c>
+      <c r="BF2" s="104"/>
+      <c r="BG2" s="104"/>
+      <c r="BH2" s="104"/>
+      <c r="BI2" s="104"/>
+      <c r="BJ2" s="104"/>
+    </row>
+    <row r="3" spans="1:62" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -20478,11 +21356,67 @@
       <c r="AM3" s="104">
         <v>3030</v>
       </c>
-      <c r="AN3" s="122"/>
-      <c r="AO3" s="122"/>
-      <c r="AP3" s="122"/>
-    </row>
-    <row r="4" spans="1:42" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AN3" s="104">
+        <v>2656</v>
+      </c>
+      <c r="AO3" s="104">
+        <v>2292</v>
+      </c>
+      <c r="AP3" s="104">
+        <v>2072</v>
+      </c>
+      <c r="AQ3" s="104">
+        <v>2043</v>
+      </c>
+      <c r="AR3" s="104">
+        <v>1651</v>
+      </c>
+      <c r="AS3" s="104">
+        <v>2503</v>
+      </c>
+      <c r="AT3" s="104">
+        <v>3090</v>
+      </c>
+      <c r="AU3" s="104">
+        <v>2989</v>
+      </c>
+      <c r="AV3" s="104">
+        <v>2657</v>
+      </c>
+      <c r="AW3" s="104">
+        <v>2862</v>
+      </c>
+      <c r="AX3" s="104">
+        <v>3396</v>
+      </c>
+      <c r="AY3" s="104">
+        <v>3198</v>
+      </c>
+      <c r="AZ3" s="104">
+        <v>3005</v>
+      </c>
+      <c r="BA3" s="104">
+        <v>3676</v>
+      </c>
+      <c r="BB3" s="104">
+        <v>4077</v>
+      </c>
+      <c r="BC3" s="104">
+        <v>4360</v>
+      </c>
+      <c r="BD3" s="104">
+        <v>4070</v>
+      </c>
+      <c r="BE3" s="104">
+        <v>3620</v>
+      </c>
+      <c r="BF3" s="104"/>
+      <c r="BG3" s="104"/>
+      <c r="BH3" s="104"/>
+      <c r="BI3" s="104"/>
+      <c r="BJ3" s="104"/>
+    </row>
+    <row r="4" spans="1:62" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -20592,11 +21526,67 @@
       <c r="AM4" s="104">
         <v>626</v>
       </c>
-      <c r="AN4" s="122"/>
-      <c r="AO4" s="122"/>
-      <c r="AP4" s="122"/>
-    </row>
-    <row r="5" spans="1:42" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AN4" s="104">
+        <v>843</v>
+      </c>
+      <c r="AO4" s="104">
+        <v>766</v>
+      </c>
+      <c r="AP4" s="104">
+        <v>548</v>
+      </c>
+      <c r="AQ4" s="104">
+        <v>588</v>
+      </c>
+      <c r="AR4" s="104">
+        <v>770</v>
+      </c>
+      <c r="AS4" s="104">
+        <v>486</v>
+      </c>
+      <c r="AT4" s="104">
+        <v>481</v>
+      </c>
+      <c r="AU4" s="104">
+        <v>479</v>
+      </c>
+      <c r="AV4" s="104">
+        <v>882</v>
+      </c>
+      <c r="AW4" s="104">
+        <v>885</v>
+      </c>
+      <c r="AX4" s="104">
+        <v>836</v>
+      </c>
+      <c r="AY4" s="104">
+        <v>898</v>
+      </c>
+      <c r="AZ4" s="104">
+        <v>729</v>
+      </c>
+      <c r="BA4" s="104">
+        <v>773</v>
+      </c>
+      <c r="BB4" s="104">
+        <v>833</v>
+      </c>
+      <c r="BC4" s="104">
+        <v>783</v>
+      </c>
+      <c r="BD4" s="104">
+        <v>838</v>
+      </c>
+      <c r="BE4" s="104">
+        <v>574</v>
+      </c>
+      <c r="BF4" s="104"/>
+      <c r="BG4" s="104"/>
+      <c r="BH4" s="104"/>
+      <c r="BI4" s="104"/>
+      <c r="BJ4" s="104"/>
+    </row>
+    <row r="5" spans="1:62" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
@@ -20706,11 +21696,67 @@
       <c r="AM5" s="104">
         <v>473</v>
       </c>
-      <c r="AN5" s="122"/>
-      <c r="AO5" s="122"/>
-      <c r="AP5" s="122"/>
-    </row>
-    <row r="6" spans="1:42" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AN5" s="104">
+        <v>539</v>
+      </c>
+      <c r="AO5" s="104">
+        <v>490</v>
+      </c>
+      <c r="AP5" s="104">
+        <v>572</v>
+      </c>
+      <c r="AQ5" s="104">
+        <v>704</v>
+      </c>
+      <c r="AR5" s="104">
+        <v>650</v>
+      </c>
+      <c r="AS5" s="104">
+        <v>846</v>
+      </c>
+      <c r="AT5" s="104">
+        <v>605</v>
+      </c>
+      <c r="AU5" s="104">
+        <v>523</v>
+      </c>
+      <c r="AV5" s="104">
+        <v>646</v>
+      </c>
+      <c r="AW5" s="104">
+        <v>580</v>
+      </c>
+      <c r="AX5" s="104">
+        <v>788</v>
+      </c>
+      <c r="AY5" s="104">
+        <v>530</v>
+      </c>
+      <c r="AZ5" s="104">
+        <v>499</v>
+      </c>
+      <c r="BA5" s="104">
+        <v>568</v>
+      </c>
+      <c r="BB5" s="104">
+        <v>479</v>
+      </c>
+      <c r="BC5" s="104">
+        <v>666</v>
+      </c>
+      <c r="BD5" s="104">
+        <v>599</v>
+      </c>
+      <c r="BE5" s="104">
+        <v>545</v>
+      </c>
+      <c r="BF5" s="104"/>
+      <c r="BG5" s="104"/>
+      <c r="BH5" s="104"/>
+      <c r="BI5" s="104"/>
+      <c r="BJ5" s="104"/>
+    </row>
+    <row r="6" spans="1:62" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -20820,11 +21866,67 @@
       <c r="AM6" s="104">
         <v>126</v>
       </c>
-      <c r="AN6" s="122"/>
-      <c r="AO6" s="122"/>
-      <c r="AP6" s="122"/>
-    </row>
-    <row r="7" spans="1:42" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AN6" s="104">
+        <v>149</v>
+      </c>
+      <c r="AO6" s="104">
+        <v>169</v>
+      </c>
+      <c r="AP6" s="104">
+        <v>244</v>
+      </c>
+      <c r="AQ6" s="104">
+        <v>278</v>
+      </c>
+      <c r="AR6" s="104">
+        <v>286</v>
+      </c>
+      <c r="AS6" s="104">
+        <v>291</v>
+      </c>
+      <c r="AT6" s="104">
+        <v>245</v>
+      </c>
+      <c r="AU6" s="104">
+        <v>260</v>
+      </c>
+      <c r="AV6" s="104">
+        <v>262</v>
+      </c>
+      <c r="AW6" s="104">
+        <v>253</v>
+      </c>
+      <c r="AX6" s="104">
+        <v>264</v>
+      </c>
+      <c r="AY6" s="104">
+        <v>222</v>
+      </c>
+      <c r="AZ6" s="104">
+        <v>255</v>
+      </c>
+      <c r="BA6" s="104">
+        <v>249</v>
+      </c>
+      <c r="BB6" s="104">
+        <v>200</v>
+      </c>
+      <c r="BC6" s="104">
+        <v>243</v>
+      </c>
+      <c r="BD6" s="104">
+        <v>255</v>
+      </c>
+      <c r="BE6" s="104">
+        <v>306</v>
+      </c>
+      <c r="BF6" s="104"/>
+      <c r="BG6" s="104"/>
+      <c r="BH6" s="104"/>
+      <c r="BI6" s="104"/>
+      <c r="BJ6" s="104"/>
+    </row>
+    <row r="7" spans="1:62" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -20934,11 +22036,67 @@
       <c r="AM7" s="104">
         <v>3436</v>
       </c>
-      <c r="AN7" s="122"/>
-      <c r="AO7" s="122"/>
-      <c r="AP7" s="122"/>
-    </row>
-    <row r="8" spans="1:42" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AN7" s="104">
+        <v>3135</v>
+      </c>
+      <c r="AO7" s="104">
+        <v>2981</v>
+      </c>
+      <c r="AP7" s="104">
+        <v>3436</v>
+      </c>
+      <c r="AQ7" s="104">
+        <v>3657</v>
+      </c>
+      <c r="AR7" s="104">
+        <v>3882</v>
+      </c>
+      <c r="AS7" s="104">
+        <v>4320</v>
+      </c>
+      <c r="AT7" s="104">
+        <v>4739</v>
+      </c>
+      <c r="AU7" s="104">
+        <v>5256</v>
+      </c>
+      <c r="AV7" s="104">
+        <v>5232</v>
+      </c>
+      <c r="AW7" s="104">
+        <v>5296</v>
+      </c>
+      <c r="AX7" s="104">
+        <v>5321</v>
+      </c>
+      <c r="AY7" s="104">
+        <v>5135</v>
+      </c>
+      <c r="AZ7" s="104">
+        <v>5293</v>
+      </c>
+      <c r="BA7" s="104">
+        <v>5372</v>
+      </c>
+      <c r="BB7" s="104">
+        <v>5045</v>
+      </c>
+      <c r="BC7" s="104">
+        <v>4878</v>
+      </c>
+      <c r="BD7" s="104">
+        <v>4900</v>
+      </c>
+      <c r="BE7" s="104">
+        <v>4885</v>
+      </c>
+      <c r="BF7" s="104"/>
+      <c r="BG7" s="104"/>
+      <c r="BH7" s="104"/>
+      <c r="BI7" s="104"/>
+      <c r="BJ7" s="104"/>
+    </row>
+    <row r="8" spans="1:62" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
@@ -21048,11 +22206,67 @@
       <c r="AM8" s="104">
         <v>457</v>
       </c>
-      <c r="AN8" s="122"/>
-      <c r="AO8" s="122"/>
-      <c r="AP8" s="122"/>
-    </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="AN8" s="104">
+        <v>492</v>
+      </c>
+      <c r="AO8" s="104">
+        <v>535</v>
+      </c>
+      <c r="AP8" s="104">
+        <v>572</v>
+      </c>
+      <c r="AQ8" s="104">
+        <v>750</v>
+      </c>
+      <c r="AR8" s="104">
+        <v>710</v>
+      </c>
+      <c r="AS8" s="104">
+        <v>726</v>
+      </c>
+      <c r="AT8" s="104">
+        <v>637</v>
+      </c>
+      <c r="AU8" s="104">
+        <v>648</v>
+      </c>
+      <c r="AV8" s="104">
+        <v>710</v>
+      </c>
+      <c r="AW8" s="104">
+        <v>646</v>
+      </c>
+      <c r="AX8" s="104">
+        <v>651</v>
+      </c>
+      <c r="AY8" s="104">
+        <v>515</v>
+      </c>
+      <c r="AZ8" s="104">
+        <v>472</v>
+      </c>
+      <c r="BA8" s="104">
+        <v>559</v>
+      </c>
+      <c r="BB8" s="104">
+        <v>414</v>
+      </c>
+      <c r="BC8" s="104">
+        <v>549</v>
+      </c>
+      <c r="BD8" s="104">
+        <v>573</v>
+      </c>
+      <c r="BE8" s="104">
+        <v>541</v>
+      </c>
+      <c r="BF8" s="104"/>
+      <c r="BG8" s="104"/>
+      <c r="BH8" s="104"/>
+      <c r="BI8" s="104"/>
+      <c r="BJ8" s="104"/>
+    </row>
+    <row r="10" spans="1:62" x14ac:dyDescent="0.25">
       <c r="L10" t="s">
         <v>9</v>
       </c>
@@ -22302,460 +23516,676 @@
       <c r="A50" s="115">
         <v>46071</v>
       </c>
-      <c r="B50" s="118"/>
-      <c r="C50" s="118"/>
-      <c r="D50" s="108" t="e">
+      <c r="B50" s="118">
+        <v>3029</v>
+      </c>
+      <c r="C50" s="118">
+        <v>214</v>
+      </c>
+      <c r="D50" s="108">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E50" s="119"/>
-      <c r="F50" s="110" t="e">
+        <v>7.0650379663255203</v>
+      </c>
+      <c r="E50" s="119">
+        <v>3</v>
+      </c>
+      <c r="F50" s="110">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G50" s="118"/>
+        <v>9.9042588312974578E-2</v>
+      </c>
+      <c r="G50" s="118">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="115">
         <v>46072</v>
       </c>
-      <c r="B51" s="118"/>
-      <c r="C51" s="118"/>
-      <c r="D51" s="108" t="e">
+      <c r="B51" s="118">
+        <v>2649</v>
+      </c>
+      <c r="C51" s="118">
+        <v>252</v>
+      </c>
+      <c r="D51" s="108">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E51" s="119"/>
-      <c r="F51" s="110" t="e">
+        <v>9.5130237825594559</v>
+      </c>
+      <c r="E51" s="119">
+        <v>4</v>
+      </c>
+      <c r="F51" s="110">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G51" s="118"/>
+        <v>0.15100037750094375</v>
+      </c>
+      <c r="G51" s="118">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="115">
         <v>46073</v>
       </c>
-      <c r="B52" s="118"/>
-      <c r="C52" s="118"/>
-      <c r="D52" s="108" t="e">
+      <c r="B52" s="118">
+        <v>2286</v>
+      </c>
+      <c r="C52" s="118">
+        <v>238</v>
+      </c>
+      <c r="D52" s="108">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E52" s="119"/>
-      <c r="F52" s="110" t="e">
+        <v>10.411198600174979</v>
+      </c>
+      <c r="E52" s="119">
+        <v>0</v>
+      </c>
+      <c r="F52" s="110">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G52" s="118"/>
+        <v>0</v>
+      </c>
+      <c r="G52" s="118">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="114">
         <v>46074</v>
       </c>
-      <c r="B53" s="116"/>
-      <c r="C53" s="116"/>
-      <c r="D53" s="100" t="e">
+      <c r="B53" s="116">
+        <v>2077</v>
+      </c>
+      <c r="C53" s="116">
+        <v>229</v>
+      </c>
+      <c r="D53" s="100">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E53" s="117"/>
-      <c r="F53" s="102" t="e">
+        <v>11.025517573423206</v>
+      </c>
+      <c r="E53" s="117">
+        <v>0</v>
+      </c>
+      <c r="F53" s="102">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G53" s="116"/>
+        <v>0</v>
+      </c>
+      <c r="G53" s="116">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="114">
         <v>46075</v>
       </c>
-      <c r="B54" s="116"/>
-      <c r="C54" s="116"/>
-      <c r="D54" s="100" t="e">
+      <c r="B54" s="116">
+        <v>2077</v>
+      </c>
+      <c r="C54" s="116">
+        <v>263</v>
+      </c>
+      <c r="D54" s="100">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E54" s="117"/>
-      <c r="F54" s="102" t="e">
+        <v>12.662493981704381</v>
+      </c>
+      <c r="E54" s="117">
+        <v>0</v>
+      </c>
+      <c r="F54" s="102">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G54" s="116"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="116">
+        <v>7.4</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="115">
         <v>46076</v>
       </c>
-      <c r="B55" s="118"/>
-      <c r="C55" s="118"/>
-      <c r="D55" s="108" t="e">
+      <c r="B55" s="118">
+        <v>2077</v>
+      </c>
+      <c r="C55" s="118">
+        <v>275</v>
+      </c>
+      <c r="D55" s="108">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E55" s="119"/>
-      <c r="F55" s="110" t="e">
+        <v>13.240250361097738</v>
+      </c>
+      <c r="E55" s="119">
+        <v>2</v>
+      </c>
+      <c r="F55" s="110">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G55" s="118"/>
+        <v>9.6292729898892634E-2</v>
+      </c>
+      <c r="G55" s="118">
+        <v>8.4</v>
+      </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="115">
         <v>46077</v>
       </c>
-      <c r="B56" s="118"/>
-      <c r="C56" s="118"/>
-      <c r="D56" s="108" t="e">
+      <c r="B56" s="118">
+        <v>2045</v>
+      </c>
+      <c r="C56" s="118">
+        <v>203</v>
+      </c>
+      <c r="D56" s="108">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E56" s="119"/>
-      <c r="F56" s="110" t="e">
+        <v>9.9266503667481665</v>
+      </c>
+      <c r="E56" s="119">
+        <v>1</v>
+      </c>
+      <c r="F56" s="110">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G56" s="118"/>
+        <v>4.889975550122249E-2</v>
+      </c>
+      <c r="G56" s="118">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="115">
         <v>46078</v>
       </c>
-      <c r="B57" s="118"/>
-      <c r="C57" s="118"/>
-      <c r="D57" s="108" t="e">
+      <c r="B57" s="118">
+        <v>1659</v>
+      </c>
+      <c r="C57" s="118">
+        <v>214</v>
+      </c>
+      <c r="D57" s="108">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E57" s="119"/>
-      <c r="F57" s="110" t="e">
+        <v>12.899336949969861</v>
+      </c>
+      <c r="E57" s="119">
+        <v>1</v>
+      </c>
+      <c r="F57" s="110">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G57" s="118"/>
+        <v>6.027727546714888E-2</v>
+      </c>
+      <c r="G57" s="118">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="115">
         <v>46079</v>
       </c>
-      <c r="B58" s="118"/>
-      <c r="C58" s="118"/>
-      <c r="D58" s="108" t="e">
+      <c r="B58" s="118">
+        <v>2501</v>
+      </c>
+      <c r="C58" s="118">
+        <v>203</v>
+      </c>
+      <c r="D58" s="108">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E58" s="119"/>
-      <c r="F58" s="110" t="e">
+        <v>8.1167532986805284</v>
+      </c>
+      <c r="E58" s="119">
+        <v>2</v>
+      </c>
+      <c r="F58" s="110">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G58" s="118"/>
+        <v>7.9968012794882054E-2</v>
+      </c>
+      <c r="G58" s="118">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="115">
         <v>46080</v>
       </c>
-      <c r="B59" s="118"/>
-      <c r="C59" s="118"/>
-      <c r="D59" s="108" t="e">
+      <c r="B59" s="118">
+        <v>3069</v>
+      </c>
+      <c r="C59" s="118">
+        <v>225</v>
+      </c>
+      <c r="D59" s="108">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E59" s="119"/>
-      <c r="F59" s="110" t="e">
+        <v>7.3313782991202352</v>
+      </c>
+      <c r="E59" s="119">
+        <v>1</v>
+      </c>
+      <c r="F59" s="110">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G59" s="118"/>
+        <v>3.2583903551645491E-2</v>
+      </c>
+      <c r="G59" s="118">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="114">
         <v>46081</v>
       </c>
-      <c r="B60" s="116"/>
-      <c r="C60" s="116"/>
-      <c r="D60" s="100" t="e">
+      <c r="B60" s="116">
+        <v>2989</v>
+      </c>
+      <c r="C60" s="116">
+        <v>226</v>
+      </c>
+      <c r="D60" s="100">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E60" s="117"/>
-      <c r="F60" s="102" t="e">
+        <v>7.561057209769154</v>
+      </c>
+      <c r="E60" s="117">
+        <v>4</v>
+      </c>
+      <c r="F60" s="102">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G60" s="116"/>
+        <v>0.13382402141184344</v>
+      </c>
+      <c r="G60" s="116">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="114">
         <v>46082</v>
       </c>
-      <c r="B61" s="116"/>
-      <c r="C61" s="116"/>
-      <c r="D61" s="100" t="e">
+      <c r="B61" s="116">
+        <v>2989</v>
+      </c>
+      <c r="C61" s="116">
+        <v>261</v>
+      </c>
+      <c r="D61" s="100">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E61" s="117"/>
-      <c r="F61" s="102" t="e">
+        <v>8.7320173971227835</v>
+      </c>
+      <c r="E61" s="117">
+        <v>5</v>
+      </c>
+      <c r="F61" s="102">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G61" s="116"/>
+        <v>0.16728002676480427</v>
+      </c>
+      <c r="G61" s="116">
+        <v>7.1</v>
+      </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="115">
         <v>46083</v>
       </c>
-      <c r="B62" s="118"/>
-      <c r="C62" s="118"/>
-      <c r="D62" s="108" t="e">
+      <c r="B62" s="118">
+        <v>2989</v>
+      </c>
+      <c r="C62" s="118">
+        <v>264</v>
+      </c>
+      <c r="D62" s="108">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E62" s="119"/>
-      <c r="F62" s="110" t="e">
+        <v>8.832385413181667</v>
+      </c>
+      <c r="E62" s="119">
+        <v>6</v>
+      </c>
+      <c r="F62" s="110">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G62" s="118"/>
+        <v>0.20073603211776514</v>
+      </c>
+      <c r="G62" s="118">
+        <v>8.1</v>
+      </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="115">
         <v>46084</v>
       </c>
-      <c r="B63" s="118"/>
-      <c r="C63" s="118"/>
-      <c r="D63" s="108" t="e">
+      <c r="B63" s="118">
+        <v>2663</v>
+      </c>
+      <c r="C63" s="118">
+        <v>194</v>
+      </c>
+      <c r="D63" s="108">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E63" s="119"/>
-      <c r="F63" s="110" t="e">
+        <v>7.2850168982350736</v>
+      </c>
+      <c r="E63" s="119">
+        <v>7</v>
+      </c>
+      <c r="F63" s="110">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G63" s="118"/>
+        <v>0.26286143447239957</v>
+      </c>
+      <c r="G63" s="118">
+        <v>8.1</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="115">
         <v>46085</v>
       </c>
-      <c r="B64" s="118"/>
-      <c r="C64" s="118"/>
-      <c r="D64" s="108" t="e">
+      <c r="B64" s="118">
+        <v>2866</v>
+      </c>
+      <c r="C64" s="118">
+        <v>183</v>
+      </c>
+      <c r="D64" s="108">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E64" s="119"/>
-      <c r="F64" s="110" t="e">
+        <v>6.3852058618283314</v>
+      </c>
+      <c r="E64" s="119">
+        <v>6</v>
+      </c>
+      <c r="F64" s="110">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G64" s="118"/>
+        <v>0.20935101186322402</v>
+      </c>
+      <c r="G64" s="118">
+        <v>7.7</v>
+      </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="115">
         <v>46086</v>
       </c>
-      <c r="B65" s="118"/>
-      <c r="C65" s="118"/>
-      <c r="D65" s="108" t="e">
+      <c r="B65" s="118">
+        <v>3404</v>
+      </c>
+      <c r="C65" s="118">
+        <v>214</v>
+      </c>
+      <c r="D65" s="108">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E65" s="119"/>
-      <c r="F65" s="110" t="e">
+        <v>6.2867215041128093</v>
+      </c>
+      <c r="E65" s="119">
+        <v>0</v>
+      </c>
+      <c r="F65" s="110">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G65" s="118"/>
+        <v>0</v>
+      </c>
+      <c r="G65" s="118">
+        <v>6.8</v>
+      </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="115">
         <v>46087</v>
       </c>
-      <c r="B66" s="118"/>
-      <c r="C66" s="118"/>
-      <c r="D66" s="108" t="e">
+      <c r="B66" s="118">
+        <v>3010</v>
+      </c>
+      <c r="C66" s="118">
+        <v>177</v>
+      </c>
+      <c r="D66" s="108">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E66" s="119"/>
-      <c r="F66" s="110" t="e">
+        <v>5.8803986710963461</v>
+      </c>
+      <c r="E66" s="119">
+        <v>2</v>
+      </c>
+      <c r="F66" s="110">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G66" s="118"/>
+        <v>6.6445182724252497E-2</v>
+      </c>
+      <c r="G66" s="118">
+        <v>6.3</v>
+      </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="115">
+      <c r="A67" s="114">
         <v>46088</v>
       </c>
-      <c r="B67" s="118"/>
-      <c r="C67" s="118"/>
-      <c r="D67" s="108" t="e">
+      <c r="B67" s="116">
+        <v>3010</v>
+      </c>
+      <c r="C67" s="116">
+        <v>223</v>
+      </c>
+      <c r="D67" s="100">
         <f t="shared" ref="D67:D130" si="2">C67/B67*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E67" s="119"/>
-      <c r="F67" s="110" t="e">
+        <v>7.4086378737541523</v>
+      </c>
+      <c r="E67" s="117">
+        <v>3</v>
+      </c>
+      <c r="F67" s="102">
         <f t="shared" ref="F67:F130" si="3">E67/B67*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G67" s="118"/>
+        <v>9.9667774086378724E-2</v>
+      </c>
+      <c r="G67" s="116">
+        <v>7.3</v>
+      </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="115">
+      <c r="A68" s="114">
         <v>46089</v>
       </c>
-      <c r="B68" s="118"/>
-      <c r="C68" s="118"/>
-      <c r="D68" s="108" t="e">
+      <c r="B68" s="116">
+        <v>3010</v>
+      </c>
+      <c r="C68" s="116">
+        <v>229</v>
+      </c>
+      <c r="D68" s="100">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E68" s="119"/>
-      <c r="F68" s="110" t="e">
+        <v>7.6079734219269097</v>
+      </c>
+      <c r="E68" s="117">
+        <v>4</v>
+      </c>
+      <c r="F68" s="102">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G68" s="118"/>
+        <v>0.13289036544850499</v>
+      </c>
+      <c r="G68" s="116">
+        <v>8.3000000000000007</v>
+      </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="115">
         <v>46090</v>
       </c>
-      <c r="B69" s="118"/>
-      <c r="C69" s="118"/>
-      <c r="D69" s="108" t="e">
+      <c r="B69" s="118">
+        <v>3010</v>
+      </c>
+      <c r="C69" s="118">
+        <v>229</v>
+      </c>
+      <c r="D69" s="108">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E69" s="119"/>
-      <c r="F69" s="110" t="e">
+        <v>7.6079734219269097</v>
+      </c>
+      <c r="E69" s="119">
+        <v>4</v>
+      </c>
+      <c r="F69" s="110">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G69" s="118"/>
+        <v>0.13289036544850499</v>
+      </c>
+      <c r="G69" s="118">
+        <v>8.3000000000000007</v>
+      </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="115">
         <v>46091</v>
       </c>
-      <c r="B70" s="118"/>
-      <c r="C70" s="118"/>
-      <c r="D70" s="108" t="e">
+      <c r="B70" s="118">
+        <v>3691</v>
+      </c>
+      <c r="C70" s="118">
+        <v>168</v>
+      </c>
+      <c r="D70" s="108">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E70" s="119"/>
-      <c r="F70" s="110" t="e">
+        <v>4.5516120292603626</v>
+      </c>
+      <c r="E70" s="119">
+        <v>4</v>
+      </c>
+      <c r="F70" s="110">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G70" s="118"/>
+        <v>0.10837171498238959</v>
+      </c>
+      <c r="G70" s="118">
+        <v>7.7</v>
+      </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="115">
         <v>46092</v>
       </c>
-      <c r="B71" s="118"/>
-      <c r="C71" s="118"/>
-      <c r="D71" s="108" t="e">
+      <c r="B71" s="118">
+        <v>4075</v>
+      </c>
+      <c r="C71" s="118">
+        <v>159</v>
+      </c>
+      <c r="D71" s="108">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E71" s="119"/>
-      <c r="F71" s="110" t="e">
+        <v>3.9018404907975457</v>
+      </c>
+      <c r="E71" s="119">
+        <v>1</v>
+      </c>
+      <c r="F71" s="110">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G71" s="118"/>
+        <v>2.4539877300613498E-2</v>
+      </c>
+      <c r="G71" s="118">
+        <v>7</v>
+      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="115">
         <v>46093</v>
       </c>
-      <c r="B72" s="118"/>
-      <c r="C72" s="118"/>
-      <c r="D72" s="108" t="e">
+      <c r="B72" s="118">
+        <v>4376</v>
+      </c>
+      <c r="C72" s="118">
+        <v>153</v>
+      </c>
+      <c r="D72" s="108">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E72" s="119"/>
-      <c r="F72" s="110" t="e">
+        <v>3.4963436928702012</v>
+      </c>
+      <c r="E72" s="119">
+        <v>1</v>
+      </c>
+      <c r="F72" s="110">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G72" s="118"/>
+        <v>2.2851919561243144E-2</v>
+      </c>
+      <c r="G72" s="118">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="115">
         <v>46094</v>
       </c>
-      <c r="B73" s="118"/>
-      <c r="C73" s="118"/>
-      <c r="D73" s="108" t="e">
+      <c r="B73" s="118">
+        <v>4074</v>
+      </c>
+      <c r="C73" s="118">
+        <v>151</v>
+      </c>
+      <c r="D73" s="108">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E73" s="119"/>
-      <c r="F73" s="110" t="e">
+        <v>3.706431026018655</v>
+      </c>
+      <c r="E73" s="119">
+        <v>1</v>
+      </c>
+      <c r="F73" s="110">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G73" s="118"/>
+        <v>2.4545900834560628E-2</v>
+      </c>
+      <c r="G73" s="118">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="115">
+      <c r="A74" s="114">
         <v>46095</v>
       </c>
-      <c r="B74" s="118"/>
-      <c r="C74" s="118"/>
-      <c r="D74" s="108" t="e">
+      <c r="B74" s="116">
+        <v>4075</v>
+      </c>
+      <c r="C74" s="116">
+        <v>173</v>
+      </c>
+      <c r="D74" s="100">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E74" s="119"/>
-      <c r="F74" s="110" t="e">
+        <v>4.2453987730061353</v>
+      </c>
+      <c r="E74" s="117">
+        <v>1</v>
+      </c>
+      <c r="F74" s="102">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G74" s="118"/>
+        <v>2.4539877300613498E-2</v>
+      </c>
+      <c r="G74" s="116">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="115">
+      <c r="A75" s="114">
         <v>46096</v>
       </c>
-      <c r="B75" s="118"/>
-      <c r="C75" s="118"/>
-      <c r="D75" s="108" t="e">
+      <c r="B75" s="116">
+        <v>4075</v>
+      </c>
+      <c r="C75" s="116">
+        <v>239</v>
+      </c>
+      <c r="D75" s="100">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E75" s="119"/>
-      <c r="F75" s="110" t="e">
+        <v>5.8650306748466257</v>
+      </c>
+      <c r="E75" s="117">
+        <v>5</v>
+      </c>
+      <c r="F75" s="102">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G75" s="118"/>
+        <v>0.1226993865030675</v>
+      </c>
+      <c r="G75" s="116">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="115">
         <v>46097</v>
       </c>
-      <c r="B76" s="118"/>
-      <c r="C76" s="118"/>
-      <c r="D76" s="108" t="e">
+      <c r="B76" s="118">
+        <v>4072</v>
+      </c>
+      <c r="C76" s="118">
+        <v>250</v>
+      </c>
+      <c r="D76" s="108">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E76" s="119"/>
-      <c r="F76" s="110" t="e">
+        <v>6.139489194499018</v>
+      </c>
+      <c r="E76" s="119">
+        <v>8</v>
+      </c>
+      <c r="F76" s="110">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G76" s="118"/>
+        <v>0.19646365422396855</v>
+      </c>
+      <c r="G76" s="118">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="115">
